--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jul-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1100.77</v>
+        <v>1111.22</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>53707.59</v>
+        <v>54217.76</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1273.92</v>
+        <v>1286.02</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1372.44</v>
+        <v>1385.48</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>814.15</v>
+        <v>821.88</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1350.97</v>
+        <v>1363.8</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>927.23</v>
+        <v>936.04</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3770.8</v>
+        <v>3806.62</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3380.51</v>
+        <v>3412.62</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2148.8</v>
+        <v>2169.21</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>774.61</v>
+        <v>781.97</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2993.27</v>
+        <v>3021.7</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1393.53</v>
+        <v>1406.77</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2374.42</v>
+        <v>2396.97</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8045.39</v>
+        <v>8121.82</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>15659.58</v>
+        <v>15808.33</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1488.32</v>
+        <v>1502.46</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>19124.36</v>
+        <v>19306.02</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>853.77</v>
+        <v>861.88</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5046.91</v>
+        <v>5094.85</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3859.33</v>
+        <v>3895.99</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1375.81</v>
+        <v>1388.88</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1079.61</v>
+        <v>1089.87</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>983.98</v>
+        <v>993.33</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>836.02</v>
+        <v>839.28</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>898.99</v>
+        <v>902.5</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>45020.31</v>
+        <v>45196.05</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>39921.31</v>
+        <v>40077.15</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>848.8099999999999</v>
+        <v>852.13</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>843</v>
+        <v>846.29</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>847.09</v>
+        <v>850.39</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1285.79</v>
+        <v>1290.81</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4386.95</v>
+        <v>4404.08</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1832.66</v>
+        <v>1839.81</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1229.63</v>
+        <v>1234.43</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>920.11</v>
+        <v>923.7</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3870.55</v>
+        <v>3885.66</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>856.65</v>
+        <v>860</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1548</v>
+        <v>1554.04</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>956.36</v>
+        <v>960.1</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5638.85</v>
+        <v>5660.86</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>12445.04</v>
+        <v>12493.62</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1241.71</v>
+        <v>1246.56</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16224.63</v>
+        <v>16287.97</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>15943.51</v>
+        <v>16005.75</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3385.15</v>
+        <v>3398.37</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3295.51</v>
+        <v>3308.38</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1036.68</v>
+        <v>1040.72</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3227.59</v>
+        <v>3240.19</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3112.51</v>
+        <v>3143.81</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1127.26</v>
+        <v>1138.59</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>827.15</v>
+        <v>835.47</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>967.0700000000001</v>
+        <v>976.8</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1177.31</v>
+        <v>1189.15</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2132.35</v>
+        <v>2153.79</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1488.3</v>
+        <v>1503.27</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1693.66</v>
+        <v>1710.7</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1209.8</v>
+        <v>1221.97</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5644.53</v>
+        <v>5701.3</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>846.59</v>
+        <v>855.1</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2589</v>
+        <v>2615.04</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4859.34</v>
+        <v>4908.22</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>785.72</v>
+        <v>793.63</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8378.42</v>
+        <v>8462.690000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>7170.91</v>
+        <v>7243.03</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13318.18</v>
+        <v>13452.13</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>813.54</v>
+        <v>821.72</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2893.81</v>
+        <v>2922.91</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1222.97</v>
+        <v>1235.27</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>9664.9</v>
+        <v>9762.110000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>7830.48</v>
+        <v>7909.23</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4073.98</v>
+        <v>4114.96</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3622.53</v>
+        <v>3658.96</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>873.99</v>
+        <v>882.78</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>796.98</v>
+        <v>805</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3641.27</v>
+        <v>3677.89</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>859.01</v>
+        <v>867.61</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1324.38</v>
+        <v>1337.64</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1441.47</v>
+        <v>1455.9</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3201.52</v>
+        <v>3233.58</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1095.58</v>
+        <v>1106.55</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2853.97</v>
+        <v>2882.55</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1603.93</v>
+        <v>1619.99</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1274.34</v>
+        <v>1287.1</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>783.55</v>
+        <v>791.39</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1386.59</v>
+        <v>1400.48</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4616.48</v>
+        <v>4662.71</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3648.27</v>
+        <v>3684.8</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>894.02</v>
+        <v>902.97</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1417.78</v>
+        <v>1431.98</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3848.48</v>
+        <v>3887.02</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2202.84</v>
+        <v>2224.89</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7899.5</v>
+        <v>7978.61</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4359.86</v>
+        <v>4403.52</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>6921.65</v>
+        <v>6990.96</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4878.17</v>
+        <v>4927.02</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>7304.05</v>
+        <v>7341.27</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2863.06</v>
+        <v>2877.65</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>5141.73</v>
+        <v>5167.93</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>815.33</v>
+        <v>819.48</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2561.84</v>
+        <v>2574.9</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>828.5700000000001</v>
+        <v>832.8</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1962.82</v>
+        <v>1972.82</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2266.44</v>
+        <v>2277.99</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4073.67</v>
+        <v>4094.43</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5359.7</v>
+        <v>5387.01</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7514.49</v>
+        <v>7552.79</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1568.2</v>
+        <v>1576.19</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2057.45</v>
+        <v>2067.93</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3368.15</v>
+        <v>3385.32</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2885.62</v>
+        <v>2900.32</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>917.1</v>
+        <v>921.77</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3502.4</v>
+        <v>3520.25</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5228.78</v>
+        <v>5255.42</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4957.08</v>
+        <v>4982.34</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6724.32</v>
+        <v>6758.59</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2135.23</v>
+        <v>2146.11</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3142.7</v>
+        <v>3158.71</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>11164.22</v>
+        <v>11221.11</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3950.11</v>
+        <v>3965.49</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2123.51</v>
+        <v>2131.78</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4671.05</v>
+        <v>4689.24</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>998.3</v>
+        <v>1002.19</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>840.73</v>
+        <v>844.01</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1197.47</v>
+        <v>1202.13</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3108.67</v>
+        <v>3120.77</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>807.21</v>
+        <v>810.35</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3698.02</v>
+        <v>3712.41</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3043.23</v>
+        <v>3055.07</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2261.62</v>
+        <v>2270.43</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1106.31</v>
+        <v>1110.62</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>788.42</v>
+        <v>791.49</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>4581.2</v>
+        <v>4599.03</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>878.15</v>
+        <v>881.5700000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2440.47</v>
+        <v>2449.97</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3300.62</v>
+        <v>3313.47</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>854.98</v>
+        <v>858.3099999999999</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>5765.48</v>
+        <v>5787.93</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1260.55</v>
+        <v>1265.46</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6943.69</v>
+        <v>6970.72</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1266.21</v>
+        <v>1271.14</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>7081.5</v>
+        <v>7109.06</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3798.15</v>
+        <v>3812.94</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>841.58</v>
+        <v>844.86</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1048.92</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1082.43</v>
+        <v>1086.64</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3466.68</v>
+        <v>3480.18</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3284.37</v>
+        <v>3297.15</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2589.2</v>
+        <v>2599.28</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>961.74</v>
+        <v>965.48</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>939.53</v>
+        <v>943.1900000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>773.35</v>
+        <v>776.36</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>775.35</v>
+        <v>778.37</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>16208.12</v>
+        <v>16271.22</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1516.89</v>
+        <v>1522.8</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2215.57</v>
+        <v>2224.19</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>18974.52</v>
+        <v>19048.38</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>12741.29</v>
+        <v>12676.75</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>4063.5</v>
+        <v>4042.91</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>785.3099999999999</v>
+        <v>781.33</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>965.45</v>
+        <v>960.5599999999999</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>9412.26</v>
+        <v>9364.58</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2308.75</v>
+        <v>2297.06</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>4012.55</v>
+        <v>3992.23</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2357.84</v>
+        <v>2345.89</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>925.4400000000001</v>
+        <v>920.76</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1701.08</v>
+        <v>1692.46</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1081.06</v>
+        <v>1075.58</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>45230.77</v>
+        <v>45001.65</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1392</v>
+        <v>1384.95</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2663.21</v>
+        <v>2649.72</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>799.15</v>
+        <v>795.1</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>966.97</v>
+        <v>962.0700000000001</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1509.48</v>
+        <v>1501.84</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>6455.2</v>
+        <v>6422.5</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>7009.49</v>
+        <v>6973.98</v>
       </c>
     </row>
     <row r="178">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>95867.75</v>
+        <v>95382.12</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>21836.19</v>
+        <v>21725.57</v>
       </c>
     </row>
     <row r="180">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1144.75</v>
+        <v>1147.19</v>
       </c>
     </row>
     <row r="181">
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>3243.42</v>
+        <v>3250.33</v>
       </c>
     </row>
     <row r="182">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1068.86</v>
+        <v>1071.14</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2782.79</v>
+        <v>2788.72</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3874.08</v>
+        <v>3882.34</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>948.27</v>
+        <v>950.29</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1003.39</v>
+        <v>1005.53</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1127.47</v>
+        <v>1129.87</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>815.26</v>
+        <v>817</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1977.94</v>
+        <v>1982.16</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1027.5</v>
+        <v>1029.69</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>6902.48</v>
+        <v>6917.19</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1293.23</v>
+        <v>1295.99</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1064.46</v>
+        <v>1066.72</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4993.76</v>
+        <v>5004.41</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1301.12</v>
+        <v>1303.89</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2993.63</v>
+        <v>3000.01</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>21442.42</v>
+        <v>21488.12</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>17699.95</v>
+        <v>17737.67</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1591.65</v>
+        <v>1595.04</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3581.11</v>
+        <v>3588.74</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1072.22</v>
+        <v>1074.5</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2454.34</v>
+        <v>2470.34</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>780.59</v>
+        <v>785.6799999999999</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1355.23</v>
+        <v>1364.06</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2047.74</v>
+        <v>2061.09</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1383.65</v>
+        <v>1392.67</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2897.76</v>
+        <v>2916.65</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1196.54</v>
+        <v>1204.34</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>769.99</v>
+        <v>775.01</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>787.91</v>
+        <v>793.04</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2657.45</v>
+        <v>2674.78</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1376.31</v>
+        <v>1385.29</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2201.76</v>
+        <v>2216.12</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>6268.73</v>
+        <v>6309.6</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1434.05</v>
+        <v>1443.4</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>20807.4</v>
+        <v>20943.05</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>840.72</v>
+        <v>846.2</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>838.08</v>
+        <v>843.54</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>835.65</v>
+        <v>841.1</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>76647.38</v>
+        <v>77147.07000000001</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>774.01</v>
+        <v>779.0599999999999</v>
       </c>
     </row>
     <row r="222">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>3155.89</v>
+        <v>3176.46</v>
       </c>
     </row>
     <row r="223">
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1286.72</v>
+        <v>1295.11</v>
       </c>
     </row>
     <row r="224">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1448.05</v>
+        <v>1457.49</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1911.14</v>
+        <v>1923.6</v>
       </c>
     </row>
     <row r="226">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>3392.44</v>
+        <v>3414.56</v>
       </c>
     </row>
     <row r="227">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>940.47</v>
+        <v>946.6</v>
       </c>
     </row>
     <row r="228">
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2233.34</v>
+        <v>2247.89</v>
       </c>
     </row>
     <row r="229">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1204.71</v>
+        <v>1212.56</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2872.53</v>
+        <v>2891.25</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1606.74</v>
+        <v>1617.22</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1992.75</v>
+        <v>2005.74</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>958.97</v>
+        <v>965.23</v>
       </c>
     </row>
     <row r="234">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>13543.43</v>
+        <v>13631.72</v>
       </c>
     </row>
     <row r="235">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4216.97</v>
+        <v>4244.46</v>
       </c>
     </row>
     <row r="236">
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>802.6</v>
+        <v>804.45</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>13388.25</v>
+        <v>13418.95</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1379.92</v>
+        <v>1383.08</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1972.02</v>
+        <v>1976.54</v>
       </c>
     </row>
     <row r="240">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>4471.3</v>
+        <v>4481.56</v>
       </c>
     </row>
     <row r="241">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3408.93</v>
+        <v>3416.75</v>
       </c>
     </row>
     <row r="242">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3395.38</v>
+        <v>3403.17</v>
       </c>
     </row>
     <row r="243">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1766.11</v>
+        <v>1770.16</v>
       </c>
     </row>
     <row r="244">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1736.33</v>
+        <v>1740.32</v>
       </c>
     </row>
     <row r="245">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2292.5</v>
+        <v>2297.76</v>
       </c>
     </row>
     <row r="246">
@@ -15461,7 +15461,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>7392.65</v>
+        <v>7409.6</v>
       </c>
     </row>
     <row r="247">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1646.94</v>
+        <v>1650.72</v>
       </c>
     </row>
     <row r="248">
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1025.02</v>
+        <v>1027.37</v>
       </c>
     </row>
     <row r="249">
@@ -15644,7 +15644,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1424.9</v>
+        <v>1428.17</v>
       </c>
     </row>
     <row r="250">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4351.94</v>
+        <v>4361.92</v>
       </c>
     </row>
     <row r="251">
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1821.54</v>
+        <v>1825.72</v>
       </c>
     </row>
     <row r="252">
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2471.94</v>
+        <v>2477.6</v>
       </c>
     </row>
     <row r="253">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>4055.97</v>
+        <v>4065.27</v>
       </c>
     </row>
     <row r="254">
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>816.45</v>
+        <v>818.3200000000001</v>
       </c>
     </row>
     <row r="255">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>976.83</v>
+        <v>979.0700000000001</v>
       </c>
     </row>
     <row r="256">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2613.61</v>
+        <v>2619.6</v>
       </c>
     </row>
     <row r="257">
@@ -16132,7 +16132,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>17793.05</v>
+        <v>17833.86</v>
       </c>
     </row>
     <row r="258">
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>788.15</v>
+        <v>789.96</v>
       </c>
     </row>
     <row r="259">
@@ -16254,7 +16254,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>16228.49</v>
+        <v>16265.71</v>
       </c>
     </row>
     <row r="260">
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>2992.99</v>
+        <v>2999.85</v>
       </c>
     </row>
     <row r="261">
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1639.38</v>
+        <v>1643.14</v>
       </c>
     </row>
     <row r="262">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>938.99</v>
+        <v>941.15</v>
       </c>
     </row>
     <row r="263">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>2953.47</v>
+        <v>2960.24</v>
       </c>
     </row>
     <row r="264">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2983.33</v>
+        <v>2990.17</v>
       </c>
     </row>
     <row r="265">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1632.98</v>
+        <v>1636.72</v>
       </c>
     </row>
     <row r="266">
@@ -16681,7 +16681,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>792.92</v>
+        <v>794.73</v>
       </c>
     </row>
     <row r="267">
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>788.0599999999999</v>
+        <v>789.87</v>
       </c>
     </row>
     <row r="268">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>818.21</v>
+        <v>820.08</v>
       </c>
     </row>
     <row r="269">
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2649.31</v>
+        <v>2655.38</v>
       </c>
     </row>
     <row r="270">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>7552.46</v>
+        <v>7569.78</v>
       </c>
     </row>
     <row r="271">
@@ -16986,7 +16986,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>911.53</v>
+        <v>913.62</v>
       </c>
     </row>
     <row r="272">
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1382.54</v>
+        <v>1385.71</v>
       </c>
     </row>
     <row r="273">
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2182.59</v>
+        <v>2187.59</v>
       </c>
     </row>
     <row r="274">
@@ -17169,7 +17169,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1969.46</v>
+        <v>1982.64</v>
       </c>
     </row>
     <row r="275">
@@ -17230,7 +17230,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2106.78</v>
+        <v>2120.88</v>
       </c>
     </row>
     <row r="276">
@@ -17291,7 +17291,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2243.79</v>
+        <v>2258.81</v>
       </c>
     </row>
     <row r="277">
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1646.17</v>
+        <v>1657.18</v>
       </c>
     </row>
     <row r="278">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>5905.45</v>
+        <v>5944.98</v>
       </c>
     </row>
     <row r="279">
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1307.26</v>
+        <v>1316.01</v>
       </c>
     </row>
     <row r="280">
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1867.83</v>
+        <v>1880.33</v>
       </c>
     </row>
     <row r="281">
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2318.18</v>
+        <v>2333.69</v>
       </c>
     </row>
     <row r="282">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1016.97</v>
+        <v>1023.77</v>
       </c>
     </row>
     <row r="283">
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1559.45</v>
+        <v>1569.89</v>
       </c>
     </row>
     <row r="284">
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4294</v>
+        <v>4322.74</v>
       </c>
     </row>
     <row r="285">
@@ -17840,7 +17840,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2760.7</v>
+        <v>2779.18</v>
       </c>
     </row>
     <row r="286">
@@ -17901,7 +17901,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>787.64</v>
+        <v>792.91</v>
       </c>
     </row>
     <row r="287">
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>18652.67</v>
+        <v>18777.52</v>
       </c>
     </row>
     <row r="288">
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1216.81</v>
+        <v>1224.95</v>
       </c>
     </row>
     <row r="289">
@@ -18084,7 +18084,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>3595.25</v>
+        <v>3619.32</v>
       </c>
     </row>
     <row r="290">
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1320.54</v>
+        <v>1329.38</v>
       </c>
     </row>
     <row r="291">
@@ -18206,7 +18206,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2614.57</v>
+        <v>2632.07</v>
       </c>
     </row>
     <row r="292">
@@ -18267,7 +18267,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>11936.48</v>
+        <v>12016.37</v>
       </c>
     </row>
     <row r="293">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1500.51</v>
+        <v>1510.55</v>
       </c>
     </row>
     <row r="294">
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>792.86</v>
+        <v>798.17</v>
       </c>
     </row>
     <row r="295">
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2363.46</v>
+        <v>2379.28</v>
       </c>
     </row>
     <row r="296">
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1108.23</v>
+        <v>1115.65</v>
       </c>
     </row>
     <row r="297">
@@ -18572,7 +18572,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1101.33</v>
+        <v>1108.7</v>
       </c>
     </row>
     <row r="298">
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1798.39</v>
+        <v>1810.43</v>
       </c>
     </row>
     <row r="299">
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2870.95</v>
+        <v>2890.16</v>
       </c>
     </row>
     <row r="300">
@@ -18755,7 +18755,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>4147.22</v>
+        <v>4174.98</v>
       </c>
     </row>
     <row r="301">
@@ -18816,7 +18816,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>8081.52</v>
+        <v>8135.62</v>
       </c>
     </row>
     <row r="302">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2761.61</v>
+        <v>2780.09</v>
       </c>
     </row>
     <row r="303">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>848.8</v>
+        <v>854.48</v>
       </c>
     </row>
     <row r="304">
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>8040.42</v>
+        <v>8094.24</v>
       </c>
     </row>
     <row r="305">
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>1828.17</v>
+        <v>1840.41</v>
       </c>
     </row>
     <row r="306">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1327.01</v>
+        <v>1335.9</v>
       </c>
     </row>
     <row r="307">
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>9088.26</v>
+        <v>9149.09</v>
       </c>
     </row>
     <row r="308">
@@ -19243,7 +19243,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>6415.71</v>
+        <v>6458.65</v>
       </c>
     </row>
     <row r="309">
@@ -19304,7 +19304,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1254.17</v>
+        <v>1262.57</v>
       </c>
     </row>
     <row r="310">
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2888.05</v>
+        <v>2907.38</v>
       </c>
     </row>
     <row r="311">
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>3035.16</v>
+        <v>3055.48</v>
       </c>
     </row>
     <row r="312">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>1616.79</v>
+        <v>1627.61</v>
       </c>
     </row>
     <row r="313">
@@ -19548,7 +19548,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>8291.950000000001</v>
+        <v>8347.450000000001</v>
       </c>
     </row>
     <row r="314">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>7818.97</v>
+        <v>7871.31</v>
       </c>
     </row>
     <row r="315">
@@ -19670,7 +19670,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>4775.83</v>
+        <v>4807.8</v>
       </c>
     </row>
     <row r="316">
@@ -19731,7 +19731,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1027.95</v>
+        <v>1034.83</v>
       </c>
     </row>
     <row r="317">
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>865.13</v>
+        <v>870.92</v>
       </c>
     </row>
     <row r="318">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1134.85</v>
+        <v>1142.45</v>
       </c>
     </row>
     <row r="319">
@@ -19914,7 +19914,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>845.55</v>
+        <v>851.21</v>
       </c>
     </row>
     <row r="320">
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>26787.84</v>
+        <v>26967.14</v>
       </c>
     </row>
     <row r="321">
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>962.16</v>
+        <v>968.89</v>
       </c>
     </row>
     <row r="322">
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>790.27</v>
+        <v>795.8</v>
       </c>
     </row>
     <row r="323">
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2035.46</v>
+        <v>2049.71</v>
       </c>
     </row>
     <row r="324">
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1796.9</v>
+        <v>1809.47</v>
       </c>
     </row>
     <row r="325">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2568.23</v>
+        <v>2586.21</v>
       </c>
     </row>
     <row r="326">
@@ -20341,7 +20341,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>20270.28</v>
+        <v>20412.14</v>
       </c>
     </row>
     <row r="327">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1597.74</v>
+        <v>1608.92</v>
       </c>
     </row>
     <row r="328">
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>777.86</v>
+        <v>783.3</v>
       </c>
     </row>
     <row r="329">
@@ -20524,7 +20524,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2522.4</v>
+        <v>2540.05</v>
       </c>
     </row>
     <row r="330">
@@ -20585,7 +20585,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>5033.24</v>
+        <v>5068.46</v>
       </c>
     </row>
     <row r="331">
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>12026.36</v>
+        <v>12110.53</v>
       </c>
     </row>
     <row r="332">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1132.74</v>
+        <v>1140.67</v>
       </c>
     </row>
     <row r="333">
@@ -20768,7 +20768,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1461.54</v>
+        <v>1456.92</v>
       </c>
     </row>
     <row r="334">
@@ -20829,7 +20829,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1609.05</v>
+        <v>1603.96</v>
       </c>
     </row>
     <row r="335">
@@ -20890,7 +20890,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1342.15</v>
+        <v>1337.91</v>
       </c>
     </row>
     <row r="336">
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>6947.25</v>
+        <v>6925.31</v>
       </c>
     </row>
     <row r="337">
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1571.27</v>
+        <v>1566.31</v>
       </c>
     </row>
     <row r="338">
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1738.96</v>
+        <v>1733.47</v>
       </c>
     </row>
     <row r="339">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1244.81</v>
+        <v>1240.88</v>
       </c>
     </row>
     <row r="340">
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>773.5599999999999</v>
+        <v>771.12</v>
       </c>
     </row>
     <row r="341">
@@ -21256,7 +21256,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>954.84</v>
+        <v>951.83</v>
       </c>
     </row>
     <row r="342">
@@ -21317,7 +21317,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2182.75</v>
+        <v>2175.85</v>
       </c>
     </row>
     <row r="343">
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>3595.16</v>
+        <v>3583.8</v>
       </c>
     </row>
     <row r="344">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>800.41</v>
+        <v>797.89</v>
       </c>
     </row>
     <row r="345">
@@ -21500,7 +21500,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1452.74</v>
+        <v>1448.15</v>
       </c>
     </row>
     <row r="346">
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>6068.43</v>
+        <v>6049.26</v>
       </c>
     </row>
     <row r="347">
@@ -21622,7 +21622,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1015.27</v>
+        <v>1012.06</v>
       </c>
     </row>
     <row r="348">
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>3561.37</v>
+        <v>3550.12</v>
       </c>
     </row>
     <row r="349">
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>791.8200000000001</v>
+        <v>790.09</v>
       </c>
     </row>
     <row r="350">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2441.43</v>
+        <v>2436.12</v>
       </c>
     </row>
     <row r="351">
@@ -21866,7 +21866,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>6075.31</v>
+        <v>6062.09</v>
       </c>
     </row>
     <row r="352">
@@ -21927,7 +21927,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>786.13</v>
+        <v>784.42</v>
       </c>
     </row>
     <row r="353">
@@ -21988,7 +21988,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>4616.99</v>
+        <v>4606.95</v>
       </c>
     </row>
     <row r="354">
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1646.61</v>
+        <v>1643.02</v>
       </c>
     </row>
     <row r="355">
@@ -22110,7 +22110,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>906.22</v>
+        <v>904.25</v>
       </c>
     </row>
     <row r="356">
@@ -22171,7 +22171,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>12489.95</v>
+        <v>12462.78</v>
       </c>
     </row>
     <row r="357">
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>2225.88</v>
+        <v>2221.04</v>
       </c>
     </row>
     <row r="358">
@@ -22293,7 +22293,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2388.39</v>
+        <v>2383.19</v>
       </c>
     </row>
     <row r="359">
@@ -22354,7 +22354,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1865.03</v>
+        <v>1860.97</v>
       </c>
     </row>
     <row r="360">
@@ -22415,7 +22415,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>779.09</v>
+        <v>777.39</v>
       </c>
     </row>
     <row r="361">
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1404.82</v>
+        <v>1401.76</v>
       </c>
     </row>
     <row r="362">
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>4290.75</v>
+        <v>4282.15</v>
       </c>
     </row>
     <row r="363">
@@ -22598,7 +22598,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>773.61</v>
+        <v>772.0599999999999</v>
       </c>
     </row>
     <row r="364">
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2001.71</v>
+        <v>1997.69</v>
       </c>
     </row>
     <row r="365">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1729.71</v>
+        <v>1726.24</v>
       </c>
     </row>
     <row r="366">
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>808.47</v>
+        <v>806.85</v>
       </c>
     </row>
     <row r="367">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>8688.1</v>
+        <v>8670.68</v>
       </c>
     </row>
     <row r="368">
@@ -22903,7 +22903,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>3355.37</v>
+        <v>3348.64</v>
       </c>
     </row>
     <row r="369">
@@ -22964,7 +22964,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>770.21</v>
+        <v>768.67</v>
       </c>
     </row>
     <row r="370">
@@ -23025,7 +23025,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>3988.71</v>
+        <v>3980.71</v>
       </c>
     </row>
     <row r="371">
@@ -23086,7 +23086,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1047.73</v>
+        <v>1045.63</v>
       </c>
     </row>
     <row r="372">
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1533.16</v>
+        <v>1530.09</v>
       </c>
     </row>
     <row r="373">
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>796.74</v>
+        <v>795.15</v>
       </c>
     </row>
     <row r="374">
@@ -23269,7 +23269,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1408.92</v>
+        <v>1406.1</v>
       </c>
     </row>
     <row r="375">
@@ -23330,7 +23330,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>1740.96</v>
+        <v>1737.47</v>
       </c>
     </row>
     <row r="376">
@@ -23391,7 +23391,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1544.05</v>
+        <v>1540.95</v>
       </c>
     </row>
     <row r="377">
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>2039.4</v>
+        <v>2035.31</v>
       </c>
     </row>
     <row r="378">
@@ -23513,7 +23513,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1377.14</v>
+        <v>1374.38</v>
       </c>
     </row>
     <row r="379">
@@ -23574,7 +23574,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1397.78</v>
+        <v>1394.98</v>
       </c>
     </row>
     <row r="380">
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2358.95</v>
+        <v>2354.22</v>
       </c>
     </row>
     <row r="381">
@@ -23696,7 +23696,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>1884.12</v>
+        <v>1880.34</v>
       </c>
     </row>
     <row r="382">
@@ -23757,7 +23757,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>7490.88</v>
+        <v>7475.86</v>
       </c>
     </row>
     <row r="383">
@@ -23818,7 +23818,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1530.37</v>
+        <v>1527.3</v>
       </c>
     </row>
     <row r="384">
@@ -23879,7 +23879,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1095.57</v>
+        <v>1093.37</v>
       </c>
     </row>
     <row r="385">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1593.67</v>
+        <v>1590.47</v>
       </c>
     </row>
     <row r="386">
@@ -24001,7 +24001,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>19096.86</v>
+        <v>19058.57</v>
       </c>
     </row>
     <row r="387">
@@ -24062,7 +24062,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>6272.27</v>
+        <v>6259.69</v>
       </c>
     </row>
     <row r="388">
@@ -24123,7 +24123,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>6321.7</v>
+        <v>6309.03</v>
       </c>
     </row>
     <row r="389">
@@ -24184,7 +24184,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>3116.86</v>
+        <v>3110.61</v>
       </c>
     </row>
     <row r="390">
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>3928.84</v>
+        <v>3920.96</v>
       </c>
     </row>
     <row r="391">
@@ -24306,7 +24306,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>2065.25</v>
+        <v>2061.11</v>
       </c>
     </row>
     <row r="392">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1373.98</v>
+        <v>1371.22</v>
       </c>
     </row>
     <row r="393">
@@ -24428,7 +24428,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>7404.83</v>
+        <v>7361.96</v>
       </c>
     </row>
     <row r="394">
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>5478.85</v>
+        <v>5447.14</v>
       </c>
     </row>
     <row r="395">
@@ -24550,7 +24550,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>15509.71</v>
+        <v>15419.94</v>
       </c>
     </row>
     <row r="396">
@@ -24611,7 +24611,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>14355.16</v>
+        <v>14272.07</v>
       </c>
     </row>
     <row r="397">
@@ -24672,7 +24672,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>3360.23</v>
+        <v>3340.78</v>
       </c>
     </row>
     <row r="398">
@@ -24733,7 +24733,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>1267.59</v>
+        <v>1260.25</v>
       </c>
     </row>
     <row r="399">
@@ -24794,7 +24794,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>2482.4</v>
+        <v>2468.03</v>
       </c>
     </row>
     <row r="400">
@@ -24855,7 +24855,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>4317.33</v>
+        <v>4292.34</v>
       </c>
     </row>
     <row r="401">
@@ -24916,7 +24916,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1487.38</v>
+        <v>1478.78</v>
       </c>
     </row>
     <row r="402">
@@ -24977,7 +24977,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2827.29</v>
+        <v>2810.92</v>
       </c>
     </row>
     <row r="403">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1695.14</v>
+        <v>1685.33</v>
       </c>
     </row>
     <row r="404">
@@ -25099,7 +25099,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>2346.11</v>
+        <v>2332.53</v>
       </c>
     </row>
     <row r="405">
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>779.48</v>
+        <v>774.97</v>
       </c>
     </row>
     <row r="406">
@@ -25221,7 +25221,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>962.13</v>
+        <v>956.5599999999999</v>
       </c>
     </row>
     <row r="407">
@@ -25282,7 +25282,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2331.5</v>
+        <v>2318.01</v>
       </c>
     </row>
     <row r="408">
@@ -25343,7 +25343,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1502.36</v>
+        <v>1493.67</v>
       </c>
     </row>
     <row r="409">
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>863.83</v>
+        <v>858.83</v>
       </c>
     </row>
     <row r="410">
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1017.73</v>
+        <v>1011.84</v>
       </c>
     </row>
     <row r="411">
@@ -25526,7 +25526,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1632.23</v>
+        <v>1622.78</v>
       </c>
     </row>
     <row r="412">
@@ -25587,7 +25587,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1266.08</v>
+        <v>1258.75</v>
       </c>
     </row>
     <row r="413">
@@ -25648,7 +25648,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2564.78</v>
+        <v>2549.94</v>
       </c>
     </row>
     <row r="414">
@@ -25709,7 +25709,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2439.13</v>
+        <v>2425.01</v>
       </c>
     </row>
     <row r="415">
@@ -25770,7 +25770,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3627.61</v>
+        <v>3606.61</v>
       </c>
     </row>
     <row r="416">
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1228.17</v>
+        <v>1221.07</v>
       </c>
     </row>
     <row r="417">
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>790.87</v>
+        <v>786.29</v>
       </c>
     </row>
     <row r="418">
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>1244.06</v>
+        <v>1236.86</v>
       </c>
     </row>
     <row r="419">
@@ -26014,7 +26014,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>2791.67</v>
+        <v>2775.51</v>
       </c>
     </row>
     <row r="420">
@@ -26075,7 +26075,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>1398.54</v>
+        <v>1390.44</v>
       </c>
     </row>
     <row r="421">
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1093.57</v>
+        <v>1087.24</v>
       </c>
     </row>
     <row r="422">
@@ -26197,7 +26197,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>3176.27</v>
+        <v>3157.88</v>
       </c>
     </row>
     <row r="423">
@@ -26258,7 +26258,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>32033.22</v>
+        <v>31847.8</v>
       </c>
     </row>
     <row r="424">
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>8405.879999999999</v>
+        <v>8357.23</v>
       </c>
     </row>
     <row r="425">
@@ -26380,7 +26380,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>983.76</v>
+        <v>978.0599999999999</v>
       </c>
     </row>
     <row r="426">
@@ -26441,7 +26441,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>852.85</v>
+        <v>847.91</v>
       </c>
     </row>
     <row r="427">
@@ -26502,7 +26502,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>1669.28</v>
+        <v>1659.62</v>
       </c>
     </row>
     <row r="428">
@@ -26563,7 +26563,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>1297.02</v>
+        <v>1289.51</v>
       </c>
     </row>
     <row r="429">
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1365.98</v>
+        <v>1358.08</v>
       </c>
     </row>
     <row r="430">
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>3795.44</v>
+        <v>3773.47</v>
       </c>
     </row>
     <row r="431">
@@ -26746,7 +26746,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1424.87</v>
+        <v>1416.62</v>
       </c>
     </row>
     <row r="432">
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2540.39</v>
+        <v>2525.69</v>
       </c>
     </row>
     <row r="433">
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>2013.51</v>
+        <v>2001.86</v>
       </c>
     </row>
     <row r="434">
@@ -26929,7 +26929,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>2314.25</v>
+        <v>2300.85</v>
       </c>
     </row>
     <row r="435">
@@ -26990,7 +26990,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>3656.47</v>
+        <v>3635.31</v>
       </c>
     </row>
     <row r="436">
@@ -27051,7 +27051,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>1494.21</v>
+        <v>1485.56</v>
       </c>
     </row>
     <row r="437">
@@ -27112,7 +27112,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1254.59</v>
+        <v>1247.33</v>
       </c>
     </row>
     <row r="438">
@@ -27173,7 +27173,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>885.4299999999999</v>
+        <v>880.3099999999999</v>
       </c>
     </row>
     <row r="439">
@@ -27234,7 +27234,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2066.4</v>
+        <v>2054.44</v>
       </c>
     </row>
     <row r="440">
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1714.67</v>
+        <v>1704.75</v>
       </c>
     </row>
     <row r="441">
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>5429.82</v>
+        <v>5398.39</v>
       </c>
     </row>
     <row r="442">
@@ -27417,7 +27417,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>1339.67</v>
+        <v>1331.92</v>
       </c>
     </row>
     <row r="443">
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>1029.94</v>
+        <v>1023.98</v>
       </c>
     </row>
     <row r="444">
@@ -27539,7 +27539,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1182.12</v>
+        <v>1175.28</v>
       </c>
     </row>
     <row r="445">
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>13423.34</v>
+        <v>13206.72</v>
       </c>
     </row>
     <row r="446">
@@ -27661,7 +27661,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>1081</v>
+        <v>1063.56</v>
       </c>
     </row>
     <row r="447">
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>793.12</v>
+        <v>780.3200000000001</v>
       </c>
     </row>
     <row r="448">
@@ -27783,7 +27783,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>771.58</v>
+        <v>759.13</v>
       </c>
     </row>
     <row r="449">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>919.05</v>
+        <v>904.22</v>
       </c>
     </row>
     <row r="450">
@@ -27905,7 +27905,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>786.5</v>
+        <v>773.8099999999999</v>
       </c>
     </row>
     <row r="451">
@@ -27966,7 +27966,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>2890.25</v>
+        <v>2843.61</v>
       </c>
     </row>
     <row r="452">
@@ -28027,7 +28027,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>879.03</v>
+        <v>864.84</v>
       </c>
     </row>
     <row r="453">
@@ -28088,7 +28088,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>1118.74</v>
+        <v>1100.69</v>
       </c>
     </row>
     <row r="454">
@@ -28149,7 +28149,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>778.83</v>
+        <v>766.26</v>
       </c>
     </row>
     <row r="455">
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>3611.64</v>
+        <v>3553.36</v>
       </c>
     </row>
     <row r="456">
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1028.31</v>
+        <v>1011.71</v>
       </c>
     </row>
     <row r="457">
@@ -28332,7 +28332,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>22517.93</v>
+        <v>22154.54</v>
       </c>
     </row>
     <row r="458">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>1370.27</v>
+        <v>1348.16</v>
       </c>
     </row>
     <row r="459">
@@ -28454,7 +28454,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1512.51</v>
+        <v>1488.1</v>
       </c>
     </row>
     <row r="460">
@@ -28515,7 +28515,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>778.01</v>
+        <v>765.45</v>
       </c>
     </row>
     <row r="461">
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>6441.56</v>
+        <v>6337.61</v>
       </c>
     </row>
     <row r="462">
@@ -28637,7 +28637,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>1791.34</v>
+        <v>1762.43</v>
       </c>
     </row>
     <row r="463">
@@ -28698,7 +28698,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>1349.84</v>
+        <v>1328.06</v>
       </c>
     </row>
     <row r="464">
@@ -28759,7 +28759,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>888.12</v>
+        <v>873.79</v>
       </c>
     </row>
     <row r="465">
@@ -28820,7 +28820,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>797.63</v>
+        <v>784.75</v>
       </c>
     </row>
     <row r="466">
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>2590.35</v>
+        <v>2548.54</v>
       </c>
     </row>
     <row r="467">
@@ -28942,7 +28942,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>1744.79</v>
+        <v>1716.64</v>
       </c>
     </row>
     <row r="468">
@@ -29003,7 +29003,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>790.72</v>
+        <v>777.96</v>
       </c>
     </row>
     <row r="469">
@@ -29064,7 +29064,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>8554.42</v>
+        <v>8416.370000000001</v>
       </c>
     </row>
     <row r="470">
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>3727.15</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="471">
@@ -29186,7 +29186,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>3282.57</v>
+        <v>3229.6</v>
       </c>
     </row>
     <row r="472">
@@ -29247,7 +29247,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>2837.76</v>
+        <v>2791.97</v>
       </c>
     </row>
     <row r="473">
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>854.73</v>
+        <v>841.03</v>
       </c>
     </row>
     <row r="474">
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>1278.28</v>
+        <v>1257.79</v>
       </c>
     </row>
     <row r="475">
@@ -29430,7 +29430,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>3032.15</v>
+        <v>2983.54</v>
       </c>
     </row>
     <row r="476">
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1201.98</v>
+        <v>1182.71</v>
       </c>
     </row>
     <row r="477">
@@ -29552,7 +29552,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>2608.15</v>
+        <v>2566.33</v>
       </c>
     </row>
     <row r="478">
@@ -29613,7 +29613,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>1383.92</v>
+        <v>1361.73</v>
       </c>
     </row>
     <row r="479">
@@ -29674,7 +29674,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>1683.44</v>
+        <v>1656.45</v>
       </c>
     </row>
     <row r="480">
@@ -29735,7 +29735,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>1771.27</v>
+        <v>1742.87</v>
       </c>
     </row>
     <row r="481">
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>3573.49</v>
+        <v>3516.19</v>
       </c>
     </row>
     <row r="482">
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>3567.56</v>
+        <v>3510.36</v>
       </c>
     </row>
     <row r="483">
@@ -29918,7 +29918,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>960.12</v>
+        <v>944.72</v>
       </c>
     </row>
     <row r="484">
@@ -29979,7 +29979,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>20436.45</v>
+        <v>20108.78</v>
       </c>
     </row>
     <row r="485">
@@ -30040,7 +30040,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>2763.93</v>
+        <v>2719.62</v>
       </c>
     </row>
     <row r="486">
@@ -30101,7 +30101,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>771.1900000000001</v>
+        <v>758.8200000000001</v>
       </c>
     </row>
     <row r="487">
@@ -30162,7 +30162,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>7536.13</v>
+        <v>7415.29</v>
       </c>
     </row>
     <row r="488">
@@ -30223,7 +30223,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>927.01</v>
+        <v>912.15</v>
       </c>
     </row>
     <row r="489">
@@ -30284,7 +30284,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>1738.22</v>
+        <v>1710.35</v>
       </c>
     </row>
     <row r="490">
@@ -30345,7 +30345,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1080.11</v>
+        <v>1062.79</v>
       </c>
     </row>
     <row r="491">
@@ -30406,7 +30406,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>7363.37</v>
+        <v>7245.31</v>
       </c>
     </row>
     <row r="492">
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>3344.05</v>
+        <v>3290.43</v>
       </c>
     </row>
     <row r="493">
@@ -30528,7 +30528,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>4851.47</v>
+        <v>4773.68</v>
       </c>
     </row>
     <row r="494">
@@ -30589,7 +30589,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>2662.57</v>
+        <v>2619.88</v>
       </c>
     </row>
     <row r="495">
@@ -30650,7 +30650,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>1589.65</v>
+        <v>1564.16</v>
       </c>
     </row>
     <row r="496">
@@ -30711,7 +30711,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>3123.63</v>
+        <v>3073.54</v>
       </c>
     </row>
     <row r="497">
@@ -30772,7 +30772,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>6755.93</v>
+        <v>6677.32</v>
       </c>
     </row>
     <row r="498">
@@ -30833,7 +30833,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>1852.93</v>
+        <v>1831.37</v>
       </c>
     </row>
     <row r="499">
@@ -30894,7 +30894,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>928.64</v>
+        <v>917.83</v>
       </c>
     </row>
     <row r="500">
@@ -30955,7 +30955,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>1955.7</v>
+        <v>1932.95</v>
       </c>
     </row>
     <row r="501">
@@ -31016,7 +31016,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>2723.92</v>
+        <v>2692.23</v>
       </c>
     </row>
     <row r="502">
@@ -31077,7 +31077,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>842.67</v>
+        <v>832.86</v>
       </c>
     </row>
     <row r="503">
@@ -31138,7 +31138,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1110.53</v>
+        <v>1097.61</v>
       </c>
     </row>
     <row r="504">
@@ -31199,7 +31199,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1186.46</v>
+        <v>1172.65</v>
       </c>
     </row>
     <row r="505">
@@ -31260,7 +31260,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2858.74</v>
+        <v>2825.48</v>
       </c>
     </row>
     <row r="506">
@@ -31321,7 +31321,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>5014.52</v>
+        <v>4956.18</v>
       </c>
     </row>
     <row r="507">
@@ -31382,7 +31382,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2991.7</v>
+        <v>2956.89</v>
       </c>
     </row>
     <row r="508">
@@ -31443,7 +31443,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1444.07</v>
+        <v>1427.26</v>
       </c>
     </row>
     <row r="509">
@@ -31504,7 +31504,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>1518.24</v>
+        <v>1500.57</v>
       </c>
     </row>
     <row r="510">
@@ -31565,7 +31565,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>23753.59</v>
+        <v>23477.2</v>
       </c>
     </row>
     <row r="511">
@@ -31626,7 +31626,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>43448.53</v>
+        <v>42942.98</v>
       </c>
     </row>
     <row r="512">
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2189.49</v>
+        <v>2164.02</v>
       </c>
     </row>
     <row r="513">
@@ -31748,7 +31748,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>3922.9</v>
+        <v>3877.25</v>
       </c>
     </row>
     <row r="514">
@@ -31809,7 +31809,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>6626.38</v>
+        <v>6549.28</v>
       </c>
     </row>
     <row r="515">
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>9376.82</v>
+        <v>9267.719999999999</v>
       </c>
     </row>
     <row r="516">
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>1232.76</v>
+        <v>1218.41</v>
       </c>
     </row>
     <row r="517">
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>831.8</v>
+        <v>822.13</v>
       </c>
     </row>
     <row r="518">
@@ -32053,7 +32053,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>1853.67</v>
+        <v>1832.1</v>
       </c>
     </row>
     <row r="519">
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>1114.5</v>
+        <v>1101.53</v>
       </c>
     </row>
     <row r="520">
@@ -32175,7 +32175,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1919.91</v>
+        <v>1897.57</v>
       </c>
     </row>
     <row r="521">
@@ -32236,7 +32236,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>805.3099999999999</v>
+        <v>795.9400000000001</v>
       </c>
     </row>
     <row r="522">
@@ -32297,7 +32297,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>888.4299999999999</v>
+        <v>878.09</v>
       </c>
     </row>
     <row r="523">
@@ -32358,7 +32358,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2572.6</v>
+        <v>2542.67</v>
       </c>
     </row>
     <row r="524">
@@ -32419,7 +32419,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>1422.04</v>
+        <v>1405.49</v>
       </c>
     </row>
     <row r="525">
@@ -32480,7 +32480,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>1702.87</v>
+        <v>1683.05</v>
       </c>
     </row>
     <row r="526">
@@ -32541,7 +32541,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>6212.23</v>
+        <v>6139.95</v>
       </c>
     </row>
     <row r="527">
@@ -32602,7 +32602,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>1125</v>
+        <v>1111.91</v>
       </c>
     </row>
     <row r="528">
@@ -32663,7 +32663,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>1562.29</v>
+        <v>1553.63</v>
       </c>
     </row>
     <row r="529">
@@ -32724,7 +32724,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>2030.86</v>
+        <v>2019.6</v>
       </c>
     </row>
     <row r="530">
@@ -32785,7 +32785,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>1683.74</v>
+        <v>1674.41</v>
       </c>
     </row>
     <row r="531">
@@ -32846,7 +32846,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>1048.26</v>
+        <v>1042.45</v>
       </c>
     </row>
     <row r="532">
@@ -32907,7 +32907,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>1343.5</v>
+        <v>1336.06</v>
       </c>
     </row>
     <row r="533">
@@ -32968,7 +32968,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>2408.01</v>
+        <v>2394.66</v>
       </c>
     </row>
     <row r="534">
@@ -33029,7 +33029,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>1153.88</v>
+        <v>1147.49</v>
       </c>
     </row>
     <row r="535">
@@ -33090,7 +33090,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1435.33</v>
+        <v>1427.37</v>
       </c>
     </row>
     <row r="536">
@@ -33151,7 +33151,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>1713.76</v>
+        <v>1704.26</v>
       </c>
     </row>
     <row r="537">
@@ -33212,7 +33212,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>6311.26</v>
+        <v>6276.27</v>
       </c>
     </row>
     <row r="538">
@@ -33273,7 +33273,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>1128.53</v>
+        <v>1122.28</v>
       </c>
     </row>
     <row r="539">
@@ -33334,7 +33334,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>6698.1</v>
+        <v>6660.97</v>
       </c>
     </row>
     <row r="540">
@@ -33395,7 +33395,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>2138.34</v>
+        <v>2126.49</v>
       </c>
     </row>
     <row r="541">
@@ -33456,7 +33456,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>1043.42</v>
+        <v>1037.64</v>
       </c>
     </row>
     <row r="542">
@@ -33517,7 +33517,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2090.84</v>
+        <v>2079.25</v>
       </c>
     </row>
     <row r="543">
@@ -33578,7 +33578,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>2720.55</v>
+        <v>2705.47</v>
       </c>
     </row>
     <row r="544">
@@ -33639,7 +33639,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>781.55</v>
+        <v>777.22</v>
       </c>
     </row>
     <row r="545">
@@ -33700,7 +33700,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>2009.19</v>
+        <v>1998.05</v>
       </c>
     </row>
     <row r="546">
@@ -33761,7 +33761,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>1787.24</v>
+        <v>1777.33</v>
       </c>
     </row>
     <row r="547">
@@ -33822,7 +33822,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>3221.92</v>
+        <v>3204.06</v>
       </c>
     </row>
     <row r="548">
@@ -33883,7 +33883,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>3048.13</v>
+        <v>3031.24</v>
       </c>
     </row>
     <row r="549">
@@ -33944,7 +33944,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>1017.86</v>
+        <v>1012.22</v>
       </c>
     </row>
     <row r="550">
@@ -34005,7 +34005,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>5212.52</v>
+        <v>5183.62</v>
       </c>
     </row>
     <row r="551">
@@ -34066,7 +34066,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>1425.01</v>
+        <v>1417.1</v>
       </c>
     </row>
     <row r="552">
@@ -34127,7 +34127,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>809.62</v>
+        <v>805.13</v>
       </c>
     </row>
     <row r="553">
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>2047.74</v>
+        <v>2036.38</v>
       </c>
     </row>
     <row r="554">
@@ -34249,7 +34249,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>6505.3</v>
+        <v>6469.24</v>
       </c>
     </row>
     <row r="555">
@@ -34310,7 +34310,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>1489.85</v>
+        <v>1481.59</v>
       </c>
     </row>
     <row r="556">
@@ -34371,7 +34371,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>3407.45</v>
+        <v>3388.56</v>
       </c>
     </row>
     <row r="557">
@@ -34432,7 +34432,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1804.49</v>
+        <v>1794.48</v>
       </c>
     </row>
     <row r="558">
@@ -34493,7 +34493,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>857.0599999999999</v>
+        <v>852.3099999999999</v>
       </c>
     </row>
     <row r="559">
@@ -34554,7 +34554,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>772.73</v>
+        <v>768.45</v>
       </c>
     </row>
     <row r="560">
@@ -34615,7 +34615,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2311.79</v>
+        <v>2298.98</v>
       </c>
     </row>
     <row r="561">
@@ -34676,7 +34676,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>3117.9</v>
+        <v>3100.62</v>
       </c>
     </row>
     <row r="562">
@@ -34737,7 +34737,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>2388.17</v>
+        <v>2376.43</v>
       </c>
     </row>
     <row r="563">
@@ -34798,7 +34798,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>3750.53</v>
+        <v>3732.08</v>
       </c>
     </row>
     <row r="564">
@@ -34859,7 +34859,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>2832.06</v>
+        <v>2818.14</v>
       </c>
     </row>
     <row r="565">
@@ -34920,7 +34920,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>2274.31</v>
+        <v>2263.13</v>
       </c>
     </row>
     <row r="566">
@@ -34981,7 +34981,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>781.41</v>
+        <v>777.5700000000001</v>
       </c>
     </row>
     <row r="567">
@@ -35042,7 +35042,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>995.87</v>
+        <v>990.98</v>
       </c>
     </row>
     <row r="568">
@@ -35103,7 +35103,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>6971.5</v>
+        <v>6937.23</v>
       </c>
     </row>
     <row r="569">
@@ -35164,7 +35164,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>966.72</v>
+        <v>961.97</v>
       </c>
     </row>
     <row r="570">
@@ -35225,7 +35225,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>7504.83</v>
+        <v>7467.93</v>
       </c>
     </row>
     <row r="571">
@@ -35286,7 +35286,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>1862.59</v>
+        <v>1853.43</v>
       </c>
     </row>
     <row r="572">
@@ -35347,7 +35347,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>1165.18</v>
+        <v>1159.45</v>
       </c>
     </row>
     <row r="573">
@@ -35408,7 +35408,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1250.8</v>
+        <v>1244.65</v>
       </c>
     </row>
     <row r="574">
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>2399.89</v>
+        <v>2388.09</v>
       </c>
     </row>
     <row r="575">
@@ -35530,7 +35530,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1225.8</v>
+        <v>1219.77</v>
       </c>
     </row>
     <row r="576">
@@ -35591,7 +35591,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>1358.54</v>
+        <v>1351.86</v>
       </c>
     </row>
     <row r="577">
@@ -35652,7 +35652,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>3552.67</v>
+        <v>3535.21</v>
       </c>
     </row>
     <row r="578">
@@ -35713,7 +35713,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>3211.68</v>
+        <v>3195.89</v>
       </c>
     </row>
     <row r="579">
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>1197.01</v>
+        <v>1191.13</v>
       </c>
     </row>
     <row r="580">
@@ -35835,7 +35835,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>3323.42</v>
+        <v>3307.07</v>
       </c>
     </row>
     <row r="581">
@@ -35896,7 +35896,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>7364.94</v>
+        <v>7328.73</v>
       </c>
     </row>
     <row r="582">
@@ -35957,7 +35957,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>1107.92</v>
+        <v>1102.47</v>
       </c>
     </row>
     <row r="583">
@@ -36018,7 +36018,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>4910.53</v>
+        <v>4886.39</v>
       </c>
     </row>
     <row r="584">
@@ -36079,7 +36079,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>958.97</v>
+        <v>954.25</v>
       </c>
     </row>
     <row r="585">
@@ -36140,7 +36140,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>892</v>
+        <v>887.62</v>
       </c>
     </row>
     <row r="586">
@@ -36201,7 +36201,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>1884.28</v>
+        <v>1875.02</v>
       </c>
     </row>
     <row r="587">
@@ -36262,7 +36262,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>4950.5</v>
+        <v>4926.16</v>
       </c>
     </row>
     <row r="588">
@@ -36323,7 +36323,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>771.1</v>
+        <v>767.3099999999999</v>
       </c>
     </row>
     <row r="589">
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>4004.3</v>
+        <v>3984.61</v>
       </c>
     </row>
     <row r="590">
@@ -36445,7 +36445,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>23265.05</v>
+        <v>23150.66</v>
       </c>
     </row>
     <row r="591">
@@ -36506,7 +36506,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>929.53</v>
+        <v>924.96</v>
       </c>
     </row>
     <row r="592">
@@ -36567,7 +36567,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>1960.53</v>
+        <v>1950.89</v>
       </c>
     </row>
     <row r="593">
@@ -36628,7 +36628,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2705.9</v>
+        <v>2692.6</v>
       </c>
     </row>
     <row r="594">
@@ -36689,7 +36689,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>797.67</v>
+        <v>793.75</v>
       </c>
     </row>
     <row r="595">
@@ -36750,7 +36750,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2284.25</v>
+        <v>2273.02</v>
       </c>
     </row>
     <row r="596">
@@ -36811,7 +36811,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>1433.8</v>
+        <v>1426.75</v>
       </c>
     </row>
     <row r="597">
@@ -36872,7 +36872,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>2541.65</v>
+        <v>2558.66</v>
       </c>
     </row>
     <row r="598">
@@ -36933,7 +36933,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>3159.23</v>
+        <v>3180.38</v>
       </c>
     </row>
     <row r="599">
@@ -36994,7 +36994,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>2094.83</v>
+        <v>2108.85</v>
       </c>
     </row>
     <row r="600">
@@ -37055,7 +37055,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>4236.59</v>
+        <v>4264.95</v>
       </c>
     </row>
     <row r="601">
@@ -37116,7 +37116,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>2822.35</v>
+        <v>2841.24</v>
       </c>
     </row>
     <row r="602">
@@ -37177,7 +37177,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>773.65</v>
+        <v>778.83</v>
       </c>
     </row>
     <row r="603">
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>2879.87</v>
+        <v>2899.14</v>
       </c>
     </row>
     <row r="604">
@@ -37299,7 +37299,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>879.66</v>
+        <v>885.54</v>
       </c>
     </row>
     <row r="605">
@@ -37360,7 +37360,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>22712.51</v>
+        <v>22864.53</v>
       </c>
     </row>
     <row r="606">
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>1058.83</v>
+        <v>1065.92</v>
       </c>
     </row>
     <row r="607">
@@ -37482,7 +37482,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1301.45</v>
+        <v>1310.16</v>
       </c>
     </row>
     <row r="608">
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>769.65</v>
+        <v>774.8</v>
       </c>
     </row>
     <row r="609">
@@ -37604,7 +37604,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>2670.91</v>
+        <v>2688.79</v>
       </c>
     </row>
     <row r="610">
@@ -37665,7 +37665,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>5415.01</v>
+        <v>5451.25</v>
       </c>
     </row>
     <row r="611">
@@ -37726,7 +37726,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>1024.95</v>
+        <v>1031.81</v>
       </c>
     </row>
     <row r="612">
@@ -37787,7 +37787,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>1185.77</v>
+        <v>1193.7</v>
       </c>
     </row>
     <row r="613">
@@ -37848,7 +37848,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>3626.51</v>
+        <v>3650.78</v>
       </c>
     </row>
     <row r="614">
@@ -37909,7 +37909,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>4280.18</v>
+        <v>4308.82</v>
       </c>
     </row>
     <row r="615">
@@ -37970,7 +37970,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>1312.06</v>
+        <v>1320.84</v>
       </c>
     </row>
     <row r="616">
@@ -38031,7 +38031,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>1287.72</v>
+        <v>1296.34</v>
       </c>
     </row>
     <row r="617">
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>2107.05</v>
+        <v>2121.15</v>
       </c>
     </row>
     <row r="618">
@@ -38153,7 +38153,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>1790.81</v>
+        <v>1802.8</v>
       </c>
     </row>
     <row r="619">
@@ -38214,7 +38214,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>1977.57</v>
+        <v>1990.81</v>
       </c>
     </row>
     <row r="620">
@@ -38275,7 +38275,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>788.0700000000001</v>
+        <v>793.34</v>
       </c>
     </row>
     <row r="621">
@@ -38336,7 +38336,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>5199.99</v>
+        <v>5234.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jul-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20077,7 +20077,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -23005,7 +23005,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23554,7 +23554,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -24103,7 +24103,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26238,7 +26238,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26299,7 +26299,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26360,7 +26360,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26909,7 +26909,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27458,7 +27458,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28617,7 +28617,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29715,7 +29715,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30569,7 +30569,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30813,7 +30813,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -31423,7 +31423,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31484,7 +31484,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31911,7 +31911,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32033,7 +32033,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32155,7 +32155,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32948,7 +32948,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33985,7 +33985,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34473,7 +34473,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34717,7 +34717,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -35449,7 +35449,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35510,7 +35510,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36059,7 +36059,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36120,7 +36120,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36181,7 +36181,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36242,7 +36242,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36364,7 +36364,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36486,7 +36486,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36730,7 +36730,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36974,7 +36974,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37340,7 +37340,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38255,7 +38255,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jul-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/jul-2026.xlsx
@@ -623,7 +623,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1521,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1586,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1907,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2094,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2159,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2289,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2419,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2484,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2549,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2679,11 @@
           <t>77.399.254-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2744,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2809,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2935,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3000,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3191,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3256,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3321,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3386,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3451,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3577,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3642,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3707,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3772,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3837,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3902,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3967,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4032,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4097,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4227,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4292,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4357,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4487,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4552,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4739,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4804,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4930,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +4995,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5060,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5125,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5190,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5255,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5320,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5385,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5450,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5515,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5580,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5645,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5710,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5775,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5840,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5905,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5970,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6035,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6100,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6165,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6230,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6295,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6360,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6425,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6490,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6555,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6620,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6685,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6750,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6815,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6880,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6945,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +7010,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7075,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7140,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7205,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7270,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7335,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7400,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7526,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7652,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7778,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8148,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8213,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8278,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8343,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8530,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8595,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8660,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8725,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8790,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8855,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8920,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8985,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9050,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9115,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9180,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9245,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9310,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9375,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9440,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9505,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9570,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9635,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9700,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9765,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9891,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9956,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +10021,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10086,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10151,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10216,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10281,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10346,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10411,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10537,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10602,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10732,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10797,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10923,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10988,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +11053,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11118,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11183,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11248,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11313,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11500,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11565,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11630,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11756,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11821,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11886,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11951,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +12016,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11611,7 +12207,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11672,7 +12272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11733,7 +12337,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11916,7 +12524,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11977,7 +12589,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12038,7 +12654,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12099,7 +12719,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12160,7 +12784,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12282,7 +12910,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12343,7 +12975,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12404,7 +13040,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12526,7 +13166,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12587,7 +13231,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12648,7 +13296,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12709,7 +13361,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12770,7 +13426,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12831,7 +13491,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12953,7 +13617,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13014,7 +13682,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13075,7 +13747,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13136,7 +13812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13197,7 +13877,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13258,7 +13942,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13319,7 +14007,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13441,7 +14133,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13502,7 +14198,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13563,7 +14263,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13624,7 +14328,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13685,7 +14393,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13746,7 +14458,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13929,7 +14645,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13990,7 +14710,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14051,7 +14775,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14112,7 +14840,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14234,7 +14966,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14295,7 +15031,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14356,7 +15096,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14417,7 +15161,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14478,7 +15226,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14539,7 +15291,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14600,7 +15356,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14661,7 +15421,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14783,7 +15547,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14905,7 +15673,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15027,7 +15799,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15088,7 +15864,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15149,7 +15929,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15210,7 +15994,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15332,7 +16120,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15393,7 +16185,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15454,7 +16250,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15515,7 +16315,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15576,7 +16380,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15698,7 +16506,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15759,7 +16571,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15820,7 +16636,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15881,7 +16701,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16003,7 +16827,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16186,7 +17014,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16308,7 +17140,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16369,7 +17205,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16430,7 +17270,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16491,7 +17335,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16552,7 +17400,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16613,7 +17465,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16674,7 +17530,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16735,7 +17595,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16796,7 +17660,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16857,7 +17725,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16918,7 +17790,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16979,7 +17855,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17162,7 +18042,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17223,7 +18107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17284,7 +18172,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +18237,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +18302,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17528,7 +18428,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18493,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17650,7 +18558,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17711,7 +18623,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17772,7 +18688,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17833,7 +18753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17894,7 +18818,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17955,7 +18883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18016,7 +18948,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18077,7 +19013,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18138,7 +19078,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18199,7 +19143,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18260,7 +19208,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18321,7 +19273,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18382,7 +19338,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18504,7 +19464,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18565,7 +19529,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18626,7 +19594,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18687,7 +19659,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18748,7 +19724,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18809,7 +19789,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18870,7 +19854,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18931,7 +19919,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19053,7 +20045,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19114,7 +20110,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19236,7 +20236,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19297,7 +20301,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19358,7 +20366,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19419,7 +20431,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19480,7 +20496,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19541,7 +20561,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19602,7 +20626,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19785,7 +20813,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19846,7 +20878,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19907,7 +20943,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20029,7 +21069,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20090,7 +21134,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20151,7 +21199,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20212,7 +21264,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20273,7 +21329,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20334,7 +21394,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20456,7 +21520,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20517,7 +21585,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20639,7 +21711,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20700,7 +21776,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20761,7 +21841,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20822,7 +21906,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20883,7 +21971,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21005,7 +22097,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21066,7 +22162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21127,7 +22227,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21188,7 +22292,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21249,7 +22357,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21371,7 +22483,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21432,7 +22548,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21493,7 +22613,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21554,7 +22678,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21615,7 +22743,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21676,7 +22808,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21737,7 +22873,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21798,7 +22938,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21859,7 +23003,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21981,7 +23129,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22042,7 +23194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22103,7 +23259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22164,7 +23324,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22225,7 +23389,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22286,7 +23454,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22347,7 +23519,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22408,7 +23584,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22469,7 +23649,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22530,7 +23714,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22591,7 +23779,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22652,7 +23844,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22774,7 +23970,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22835,7 +24035,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22896,7 +24100,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22957,7 +24165,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23018,7 +24230,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23079,7 +24295,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23140,7 +24360,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23201,7 +24425,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23323,7 +24551,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23445,7 +24677,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23567,7 +24803,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23628,7 +24868,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23750,7 +24994,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23811,7 +25059,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23933,7 +25185,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24055,7 +25311,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24116,7 +25376,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24177,7 +25441,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24238,7 +25506,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24299,7 +25571,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24360,7 +25636,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24421,7 +25701,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24482,7 +25766,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24543,7 +25831,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24604,7 +25896,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24665,7 +25961,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24726,7 +26026,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24787,7 +26091,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24848,7 +26156,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +26221,11 @@
           <t>77.350.794-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24970,7 +26286,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25031,7 +26351,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25092,7 +26416,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25214,7 +26542,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25275,7 +26607,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25336,7 +26672,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25397,7 +26737,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25458,7 +26802,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25519,7 +26867,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25580,7 +26932,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25641,7 +26997,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25702,7 +27062,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25763,7 +27127,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25824,7 +27192,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25946,7 +27318,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26007,7 +27383,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26129,7 +27509,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26190,7 +27574,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26251,7 +27639,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26312,7 +27704,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26373,7 +27769,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26434,7 +27834,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26495,7 +27899,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26556,7 +27964,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26617,7 +28029,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26678,7 +28094,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26739,7 +28159,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26800,7 +28224,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26861,7 +28289,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26922,7 +28354,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26983,7 +28419,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27044,7 +28484,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27105,7 +28549,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27166,7 +28614,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27227,7 +28679,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27288,7 +28744,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27349,7 +28809,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27410,7 +28874,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27471,7 +28939,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27532,7 +29004,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27593,7 +29069,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27715,7 +29195,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27776,7 +29260,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27837,7 +29325,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27898,7 +29390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28081,7 +29577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28142,7 +29642,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28203,7 +29707,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28325,7 +29833,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28386,7 +29898,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28447,7 +29963,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28508,7 +30028,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28569,7 +30093,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28630,7 +30158,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28691,7 +30223,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28874,7 +30410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28996,7 +30536,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29057,7 +30601,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29118,7 +30666,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29240,7 +30792,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29484,7 +31040,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29545,7 +31105,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29606,7 +31170,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29667,7 +31235,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29728,7 +31300,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29789,7 +31365,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29850,7 +31430,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29911,7 +31495,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29972,7 +31560,11 @@
           <t>78.085.327-1</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30033,7 +31625,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30094,7 +31690,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30155,7 +31755,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30216,7 +31820,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30277,7 +31885,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30338,7 +31950,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30460,7 +32076,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30521,7 +32141,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30582,7 +32206,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30643,7 +32271,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30704,7 +32336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30765,7 +32401,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30948,7 +32588,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31070,7 +32714,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31192,7 +32840,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31253,7 +32905,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31314,7 +32970,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31375,7 +33035,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31436,7 +33100,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31497,7 +33165,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31558,7 +33230,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31619,7 +33295,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31680,7 +33360,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31741,7 +33425,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31863,7 +33551,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31924,7 +33616,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31985,7 +33681,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32046,7 +33746,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32107,7 +33811,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32168,7 +33876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32351,7 +34063,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32412,7 +34128,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32473,7 +34193,11 @@
           <t>77.723.304-1</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32534,7 +34258,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32595,7 +34323,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32656,7 +34388,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32717,7 +34453,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32778,7 +34518,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32839,7 +34583,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32961,7 +34709,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33022,7 +34774,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33083,7 +34839,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33144,7 +34904,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33327,7 +35091,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33388,7 +35156,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33449,7 +35221,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33510,7 +35286,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33571,7 +35351,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33632,7 +35416,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33693,7 +35481,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33754,7 +35546,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33815,7 +35611,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33876,7 +35676,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33998,7 +35802,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34059,7 +35867,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34120,7 +35932,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34181,7 +35997,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34242,7 +36062,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34303,7 +36127,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34364,7 +36192,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34425,7 +36257,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34486,7 +36322,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34547,7 +36387,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34608,7 +36452,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34669,7 +36517,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34730,7 +36582,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34974,7 +36830,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35035,7 +36895,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35096,7 +36960,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35157,7 +37025,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35218,7 +37090,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35279,7 +37155,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35401,7 +37281,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35462,7 +37346,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35523,7 +37411,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35584,7 +37476,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35645,7 +37541,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35706,7 +37606,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35767,7 +37671,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35828,7 +37736,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35889,7 +37801,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36011,7 +37927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36072,7 +37992,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36133,7 +38057,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36194,7 +38122,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36255,7 +38187,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36316,7 +38252,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36377,7 +38317,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36438,7 +38382,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36499,7 +38447,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36560,7 +38512,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36621,7 +38577,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36682,7 +38642,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36743,7 +38707,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36804,7 +38772,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36865,7 +38837,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36987,7 +38963,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37048,7 +39028,11 @@
           <t>77.042.972-2</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37109,7 +39093,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37231,7 +39219,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37353,7 +39345,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37414,7 +39410,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37536,7 +39536,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37597,7 +39601,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37658,7 +39666,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37780,7 +39792,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37841,7 +39857,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37963,7 +39983,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38024,7 +40048,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38085,7 +40113,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38146,7 +40178,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38207,7 +40243,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38329,7 +40369,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38451,7 +40495,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38512,7 +40560,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38573,7 +40625,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38695,7 +40751,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38756,7 +40816,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38817,7 +40881,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38878,7 +40946,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
